--- a/exemple/etudiants-exemple.xlsx
+++ b/exemple/etudiants-exemple.xlsx
@@ -434,7 +434,7 @@
         <v>Tranche 2</v>
       </c>
       <c r="H1" t="str">
-        <v>Echéance</v>
+        <v>Tranche 3</v>
       </c>
     </row>
     <row r="2">
@@ -445,22 +445,22 @@
         <v>KOUASSI Jean Marc</v>
       </c>
       <c r="C2">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D2">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G2" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H2" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="3">
@@ -471,22 +471,22 @@
         <v>TRAORE Awa</v>
       </c>
       <c r="C3">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D3">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G3" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H3" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="4">
@@ -497,22 +497,22 @@
         <v>KONE Ibrahim</v>
       </c>
       <c r="C4">
+        <v>460000</v>
+      </c>
+      <c r="D4">
+        <v>310000</v>
+      </c>
+      <c r="E4">
         <v>150000</v>
       </c>
-      <c r="D4">
-        <v>75000</v>
-      </c>
-      <c r="E4">
-        <v>75000</v>
-      </c>
       <c r="F4" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G4" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H4" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="5">
@@ -523,22 +523,22 @@
         <v>YAO Marie-Claire</v>
       </c>
       <c r="C5">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D5">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F5" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G5" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H5" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="6">
@@ -549,22 +549,22 @@
         <v>BAMBA Souleymane</v>
       </c>
       <c r="C6">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="F6" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G6" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H6" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="7">
@@ -575,22 +575,22 @@
         <v>N'GUESSAN Adjoua</v>
       </c>
       <c r="C7">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D7">
         <v>100000</v>
       </c>
       <c r="E7">
-        <v>50000</v>
+        <v>360000</v>
       </c>
       <c r="F7" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G7" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H7" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="8">
@@ -601,22 +601,22 @@
         <v>DIALLO Mamadou</v>
       </c>
       <c r="C8">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D8">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8" t="str">
-        <v>75 000 FCFA - 15/10/2026</v>
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="G8" t="str">
-        <v>75 000 FCFA - 15/12/2026</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="H8" t="str">
-        <v>15/12/2026</v>
+        <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
     <row r="9">
@@ -644,7 +644,7 @@
         <v/>
       </c>
       <c r="C10">
-        <v>1050000</v>
+        <v>3220000</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -699,10 +699,10 @@
         <v>COULIBALY Fatoumata</v>
       </c>
       <c r="C2">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D2">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -716,13 +716,13 @@
         <v>OUATTARA Seydou</v>
       </c>
       <c r="C3">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D3">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="E3">
-        <v>100000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="4">
@@ -733,10 +733,10 @@
         <v>AKA Kouadio Serge</v>
       </c>
       <c r="C4">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D4">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -750,13 +750,13 @@
         <v>TANOH Estelle</v>
       </c>
       <c r="C5">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D5">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>140000</v>
       </c>
     </row>
     <row r="6">
@@ -767,13 +767,13 @@
         <v>SORO Yacouba</v>
       </c>
       <c r="C6">
+        <v>300000</v>
+      </c>
+      <c r="D6">
         <v>150000</v>
       </c>
-      <c r="D6">
-        <v>100000</v>
-      </c>
       <c r="E6">
-        <v>50000</v>
+        <v>150000</v>
       </c>
     </row>
     <row r="7">
@@ -784,10 +784,10 @@
         <v>KOFFI Amenan</v>
       </c>
       <c r="C7">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D7">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -801,10 +801,10 @@
         <v>COULIBALY Fatoumata</v>
       </c>
       <c r="C8">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D8">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -818,10 +818,10 @@
         <v>SANS MATRICULE Test</v>
       </c>
       <c r="C9">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="D9">
-        <v>150000</v>
+        <v>300000</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -876,10 +876,10 @@
         <v>DOSSO Aminata</v>
       </c>
       <c r="C2">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D2">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -896,13 +896,13 @@
         <v>GBAGBO Patrick</v>
       </c>
       <c r="C3">
+        <v>460000</v>
+      </c>
+      <c r="D3">
+        <v>310000</v>
+      </c>
+      <c r="E3">
         <v>150000</v>
-      </c>
-      <c r="D3">
-        <v>150000</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
       </c>
       <c r="F3" t="str">
         <v>CAR 21</v>
@@ -916,13 +916,13 @@
         <v>ZADI Rosine</v>
       </c>
       <c r="C4">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D4">
-        <v>25000</v>
+        <v>100000</v>
       </c>
       <c r="E4">
-        <v>125000</v>
+        <v>360000</v>
       </c>
       <c r="F4" t="str">
         <v>CAR 21</v>
@@ -936,10 +936,10 @@
         <v>BROU Alain</v>
       </c>
       <c r="C5">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D5">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -956,13 +956,13 @@
         <v>FOFANA Salimata</v>
       </c>
       <c r="C6">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D6">
-        <v>150000</v>
+        <v>160000</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="F6" t="str">
         <v>CAR 21</v>
@@ -976,13 +976,13 @@
         <v>ADOU Cédric</v>
       </c>
       <c r="C7">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="F7" t="str">
         <v>CAR 21</v>
@@ -996,10 +996,10 @@
         <v>SYLLA Kadidja</v>
       </c>
       <c r="C8">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="D8">
-        <v>150000</v>
+        <v>460000</v>
       </c>
       <c r="E8">
         <v>0</v>

--- a/exemple/etudiants-exemple.xlsx
+++ b/exemple/etudiants-exemple.xlsx
@@ -399,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:G10"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -422,18 +422,15 @@
         <v>Montant</v>
       </c>
       <c r="D1" t="str">
-        <v>TOTPAYE</v>
+        <v>SOLDE</v>
       </c>
       <c r="E1" t="str">
-        <v>SOLDE</v>
+        <v>Tranche 1</v>
       </c>
       <c r="F1" t="str">
-        <v>Tranche 1</v>
+        <v>Tranche 2</v>
       </c>
       <c r="G1" t="str">
-        <v>Tranche 2</v>
-      </c>
-      <c r="H1" t="str">
         <v>Tranche 3</v>
       </c>
     </row>
@@ -448,18 +445,15 @@
         <v>460000</v>
       </c>
       <c r="D2">
-        <v>460000</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="F2" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G2" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H2" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -474,18 +468,15 @@
         <v>460000</v>
       </c>
       <c r="D3">
-        <v>460000</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E3" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="F3" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G3" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H3" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -497,21 +488,18 @@
         <v>KONE Ibrahim</v>
       </c>
       <c r="C4">
-        <v>460000</v>
+        <v>310000</v>
       </c>
       <c r="D4">
-        <v>310000</v>
-      </c>
-      <c r="E4">
         <v>150000</v>
       </c>
+      <c r="E4" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
+      </c>
       <c r="F4" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G4" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H4" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -523,21 +511,18 @@
         <v>YAO Marie-Claire</v>
       </c>
       <c r="C5">
-        <v>460000</v>
+        <v>160000</v>
       </c>
       <c r="D5">
-        <v>160000</v>
-      </c>
-      <c r="E5">
         <v>300000</v>
       </c>
+      <c r="E5" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
+      </c>
       <c r="F5" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G5" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H5" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -549,21 +534,18 @@
         <v>BAMBA Souleymane</v>
       </c>
       <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6">
         <v>460000</v>
       </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>460000</v>
+      <c r="E6" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="F6" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G6" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H6" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -575,21 +557,18 @@
         <v>N'GUESSAN Adjoua</v>
       </c>
       <c r="C7">
-        <v>460000</v>
+        <v>100000</v>
       </c>
       <c r="D7">
-        <v>100000</v>
-      </c>
-      <c r="E7">
         <v>360000</v>
       </c>
+      <c r="E7" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
+      </c>
       <c r="F7" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G7" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H7" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -604,18 +583,15 @@
         <v>460000</v>
       </c>
       <c r="D8">
-        <v>460000</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
+        <v>160 000 FCFA cumulés avant le 10/12</v>
       </c>
       <c r="F8" t="str">
-        <v>160 000 FCFA cumulés avant le 10/12</v>
+        <v>310 000 FCFA cumulés avant le 10/03</v>
       </c>
       <c r="G8" t="str">
-        <v>310 000 FCFA cumulés avant le 10/03</v>
-      </c>
-      <c r="H8" t="str">
         <v>460 000 FCFA cumulés avant fin juin</v>
       </c>
     </row>
@@ -632,9 +608,6 @@
       <c r="D9" t="str">
         <v/>
       </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -644,25 +617,22 @@
         <v/>
       </c>
       <c r="C10">
-        <v>3220000</v>
+        <v>0</v>
       </c>
       <c r="D10">
-        <v>0</v>
-      </c>
-      <c r="E10">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G10"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:D9"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -685,9 +655,6 @@
         <v>Montant</v>
       </c>
       <c r="D1" t="str">
-        <v>TOTPAYE</v>
-      </c>
-      <c r="E1" t="str">
         <v>SOLDE</v>
       </c>
     </row>
@@ -702,9 +669,6 @@
         <v>300000</v>
       </c>
       <c r="D2">
-        <v>300000</v>
-      </c>
-      <c r="E2">
         <v>0</v>
       </c>
     </row>
@@ -716,12 +680,9 @@
         <v>OUATTARA Seydou</v>
       </c>
       <c r="C3">
-        <v>300000</v>
+        <v>100000</v>
       </c>
       <c r="D3">
-        <v>100000</v>
-      </c>
-      <c r="E3">
         <v>200000</v>
       </c>
     </row>
@@ -736,9 +697,6 @@
         <v>300000</v>
       </c>
       <c r="D4">
-        <v>300000</v>
-      </c>
-      <c r="E4">
         <v>0</v>
       </c>
     </row>
@@ -750,12 +708,9 @@
         <v>TANOH Estelle</v>
       </c>
       <c r="C5">
-        <v>300000</v>
+        <v>160000</v>
       </c>
       <c r="D5">
-        <v>160000</v>
-      </c>
-      <c r="E5">
         <v>140000</v>
       </c>
     </row>
@@ -767,12 +722,9 @@
         <v>SORO Yacouba</v>
       </c>
       <c r="C6">
-        <v>300000</v>
+        <v>150000</v>
       </c>
       <c r="D6">
-        <v>150000</v>
-      </c>
-      <c r="E6">
         <v>150000</v>
       </c>
     </row>
@@ -787,9 +739,6 @@
         <v>300000</v>
       </c>
       <c r="D7">
-        <v>300000</v>
-      </c>
-      <c r="E7">
         <v>0</v>
       </c>
     </row>
@@ -804,9 +753,6 @@
         <v>300000</v>
       </c>
       <c r="D8">
-        <v>300000</v>
-      </c>
-      <c r="E8">
         <v>0</v>
       </c>
     </row>
@@ -821,22 +767,19 @@
         <v>300000</v>
       </c>
       <c r="D9">
-        <v>300000</v>
-      </c>
-      <c r="E9">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="28.83203125" customWidth="1"/>
@@ -859,12 +802,9 @@
         <v>Montant</v>
       </c>
       <c r="D1" t="str">
-        <v>TOTPAYE</v>
+        <v>SOLDE</v>
       </c>
       <c r="E1" t="str">
-        <v>SOLDE</v>
-      </c>
-      <c r="F1" t="str">
         <v>CAR</v>
       </c>
     </row>
@@ -879,12 +819,9 @@
         <v>460000</v>
       </c>
       <c r="D2">
-        <v>460000</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-      <c r="F2" t="str">
+        <v>0</v>
+      </c>
+      <c r="E2" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -896,15 +833,12 @@
         <v>GBAGBO Patrick</v>
       </c>
       <c r="C3">
-        <v>460000</v>
+        <v>310000</v>
       </c>
       <c r="D3">
-        <v>310000</v>
-      </c>
-      <c r="E3">
         <v>150000</v>
       </c>
-      <c r="F3" t="str">
+      <c r="E3" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -916,15 +850,12 @@
         <v>ZADI Rosine</v>
       </c>
       <c r="C4">
-        <v>460000</v>
+        <v>100000</v>
       </c>
       <c r="D4">
-        <v>100000</v>
-      </c>
-      <c r="E4">
         <v>360000</v>
       </c>
-      <c r="F4" t="str">
+      <c r="E4" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -939,12 +870,9 @@
         <v>460000</v>
       </c>
       <c r="D5">
-        <v>460000</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-      <c r="F5" t="str">
+        <v>0</v>
+      </c>
+      <c r="E5" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -956,15 +884,12 @@
         <v>FOFANA Salimata</v>
       </c>
       <c r="C6">
-        <v>460000</v>
+        <v>160000</v>
       </c>
       <c r="D6">
-        <v>160000</v>
-      </c>
-      <c r="E6">
         <v>300000</v>
       </c>
-      <c r="F6" t="str">
+      <c r="E6" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -976,15 +901,12 @@
         <v>ADOU Cédric</v>
       </c>
       <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
         <v>460000</v>
       </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>460000</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="E7" t="str">
         <v>CAR 21</v>
       </c>
     </row>
@@ -999,18 +921,15 @@
         <v>460000</v>
       </c>
       <c r="D8">
-        <v>460000</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="str">
+        <v>0</v>
+      </c>
+      <c r="E8" t="str">
         <v>CAR 21</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E8"/>
   </ignoredErrors>
 </worksheet>
 </file>